--- a/GameConfig/LevelSheet.xlsx
+++ b/GameConfig/LevelSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\AI Project\HTML Project\WordSort\GameConfig\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32CBEB81-37CB-49D5-98F0-2AAF59472773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30BF0E3D-DF14-47DD-8E61-4716EBE05EDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -594,13 +594,13 @@
         <v>10015</v>
       </c>
       <c r="B16" s="1">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C16" s="1">
         <v>5</v>
       </c>
       <c r="D16" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
@@ -650,13 +650,13 @@
         <v>10019</v>
       </c>
       <c r="B20" s="1">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C20" s="1">
         <v>5</v>
       </c>
       <c r="D20" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
@@ -706,13 +706,13 @@
         <v>10023</v>
       </c>
       <c r="B24" s="1">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C24" s="1">
         <v>5</v>
       </c>
       <c r="D24" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.4">
@@ -762,13 +762,13 @@
         <v>10027</v>
       </c>
       <c r="B28" s="1">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C28" s="1">
         <v>5</v>
       </c>
       <c r="D28" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
@@ -782,7 +782,7 @@
         <v>4</v>
       </c>
       <c r="D29" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.4">
@@ -796,7 +796,7 @@
         <v>4</v>
       </c>
       <c r="D30" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
@@ -810,7 +810,7 @@
         <v>5</v>
       </c>
       <c r="D31" s="1">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/GameConfig/LevelSheet.xlsx
+++ b/GameConfig/LevelSheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\AI Project\HTML Project\WordSort\GameConfig\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30BF0E3D-DF14-47DD-8E61-4716EBE05EDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B51519C-B1CA-4231-B464-A5B268D74BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -580,13 +580,13 @@
         <v>10014</v>
       </c>
       <c r="B15" s="1">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1">
         <v>5</v>
       </c>
       <c r="D15" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
@@ -636,7 +636,7 @@
         <v>10018</v>
       </c>
       <c r="B19" s="1">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C19" s="1">
         <v>5</v>
@@ -692,7 +692,7 @@
         <v>10022</v>
       </c>
       <c r="B23" s="1">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C23" s="1">
         <v>5</v>
@@ -748,7 +748,7 @@
         <v>10026</v>
       </c>
       <c r="B27" s="1">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C27" s="1">
         <v>5</v>
